--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/NORTH_CAROLINA_2018.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/NORTH_CAROLINA_2018.xlsx
@@ -427,7 +427,7 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>0.0009577233547680941</v>
+        <v>0.000957723354768094</v>
       </c>
     </row>
     <row r="5">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C177">
@@ -5773,7 +5773,7 @@
         <v>204</v>
       </c>
       <c r="D301">
-        <v>0.009303598303461487</v>
+        <v>0.009303598303461488</v>
       </c>
     </row>
     <row r="302">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C307">
@@ -7177,7 +7177,7 @@
         <v>21</v>
       </c>
       <c r="D379">
-        <v>0.0009577233547680941</v>
+        <v>0.000957723354768094</v>
       </c>
     </row>
     <row r="380">
@@ -7429,7 +7429,7 @@
         <v>21</v>
       </c>
       <c r="D393">
-        <v>0.0009577233547680941</v>
+        <v>0.000957723354768094</v>
       </c>
     </row>
     <row r="394">
@@ -8077,7 +8077,7 @@
         <v>21</v>
       </c>
       <c r="D429">
-        <v>0.0009577233547680941</v>
+        <v>0.000957723354768094</v>
       </c>
     </row>
     <row r="430">
@@ -9409,7 +9409,7 @@
         <v>21</v>
       </c>
       <c r="D503">
-        <v>0.0009577233547680941</v>
+        <v>0.000957723354768094</v>
       </c>
     </row>
     <row r="504">
@@ -13326,7 +13326,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C721">
@@ -15396,7 +15396,7 @@
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C836">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C837">
@@ -16350,7 +16350,7 @@
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C889">
@@ -16368,7 +16368,7 @@
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C890">
@@ -16753,7 +16753,7 @@
         <v>21</v>
       </c>
       <c r="D911">
-        <v>0.0009577233547680941</v>
+        <v>0.000957723354768094</v>
       </c>
     </row>
     <row r="912">
@@ -18384,7 +18384,7 @@
       </c>
       <c r="B1002" t="inlineStr">
         <is>
-          <t>Santo Domingo Tonaltepec</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C1002">
@@ -23107,7 +23107,7 @@
         <v>21</v>
       </c>
       <c r="D1264">
-        <v>0.0009577233547680941</v>
+        <v>0.000957723354768094</v>
       </c>
     </row>
     <row r="1265">
@@ -26437,7 +26437,7 @@
         <v>21</v>
       </c>
       <c r="D1449">
-        <v>0.0009577233547680941</v>
+        <v>0.000957723354768094</v>
       </c>
     </row>
     <row r="1450">
